--- a/tests/Bntu.Library.CardGenerator.Infrastructure.Tables.Tests/TestAssets/Xlsx/invalid_name.xlsx
+++ b/tests/Bntu.Library.CardGenerator.Infrastructure.Tables.Tests/TestAssets/Xlsx/invalid_name.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\repositories\BNTU-library-card-generator\tests\Bntu.Library.CardGenerator.Infrastructure.Tables.Tests\XlsxExamples\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\repositories\BNTU-library-card-generator\tests\Bntu.Library.CardGenerator.Infrastructure.Tables.Tests\TestAssets\Xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D5E70A0-53B4-4172-9CE3-96D380DF5F69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB01CACA-42A6-4E8C-98AD-8737F7ED36F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="67">
   <si>
     <t>#</t>
   </si>
@@ -44,9 +44,6 @@
     <t>Форма обучения</t>
   </si>
   <si>
-    <t>Дата начала обучения</t>
-  </si>
-  <si>
     <t>Дата окончания обучения</t>
   </si>
   <si>
@@ -146,9 +143,6 @@
     <t>девушка</t>
   </si>
   <si>
-    <t>2018-09-01</t>
-  </si>
-  <si>
     <t>2022-06-30</t>
   </si>
   <si>
@@ -240,6 +234,9 @@
   </si>
   <si>
     <t>Пол</t>
+  </si>
+  <si>
+    <t>Год поступления</t>
   </si>
 </sst>
 </file>
@@ -586,103 +583,103 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" t="s">
         <v>61</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>62</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>63</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>64</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>65</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>66</v>
       </c>
-      <c r="H1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>3</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>4</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>5</v>
-      </c>
-      <c r="M1" t="s">
-        <v>6</v>
       </c>
       <c r="N1" t="s">
         <v>1</v>
       </c>
       <c r="O1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q1" t="s">
         <v>9</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>10</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>11</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>12</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>13</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>14</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>15</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>16</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>17</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>18</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>19</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>20</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>21</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>22</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>23</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>24</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>25</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>26</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
@@ -690,73 +687,73 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s">
         <v>29</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>30</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>31</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>32</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>33</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>34</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2">
+        <v>2018</v>
+      </c>
+      <c r="J2" t="s">
         <v>35</v>
       </c>
-      <c r="I2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J2" t="s">
-        <v>37</v>
-      </c>
       <c r="K2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L2">
         <v>10101</v>
       </c>
       <c r="M2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" t="s">
         <v>38</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>39</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>40</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" t="s">
         <v>41</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="S2" t="s">
         <v>42</v>
       </c>
-      <c r="R2" t="s">
+      <c r="T2" t="s">
         <v>43</v>
       </c>
-      <c r="S2" t="s">
+      <c r="U2" t="s">
         <v>44</v>
       </c>
-      <c r="T2" t="s">
+      <c r="V2" t="s">
         <v>45</v>
       </c>
-      <c r="U2" t="s">
-        <v>46</v>
-      </c>
-      <c r="V2" t="s">
-        <v>47</v>
-      </c>
       <c r="AH2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.25">
@@ -764,64 +761,64 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" t="s">
         <v>34</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3">
+        <v>2018</v>
+      </c>
+      <c r="J3" t="s">
         <v>35</v>
       </c>
-      <c r="I3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" t="s">
-        <v>37</v>
-      </c>
       <c r="K3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L3">
         <v>20202</v>
       </c>
       <c r="M3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N3" t="s">
+        <v>49</v>
+      </c>
+      <c r="O3" t="s">
         <v>50</v>
       </c>
-      <c r="N3" t="s">
+      <c r="P3" t="s">
         <v>51</v>
       </c>
-      <c r="O3" t="s">
+      <c r="Q3" t="s">
         <v>52</v>
       </c>
-      <c r="P3" t="s">
+      <c r="R3" t="s">
+        <v>41</v>
+      </c>
+      <c r="S3" t="s">
         <v>53</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="T3" t="s">
         <v>54</v>
       </c>
-      <c r="R3" t="s">
-        <v>43</v>
-      </c>
-      <c r="S3" t="s">
+      <c r="U3" t="s">
         <v>55</v>
       </c>
-      <c r="T3" t="s">
+      <c r="V3" t="s">
         <v>56</v>
       </c>
-      <c r="U3" t="s">
-        <v>57</v>
-      </c>
-      <c r="V3" t="s">
-        <v>58</v>
-      </c>
       <c r="AH3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
